--- a/Profile Insights/Salary Details.xlsx
+++ b/Profile Insights/Salary Details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenova\OneDrive\Desktop\TestingDocumentation\Profile Insights\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8914A99-C4B8-4A8B-A581-85C3CECC7D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D24FD60-AB1B-4FED-A53F-EB47BFB698E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Current CTC Breakdown" sheetId="1" r:id="rId1"/>
@@ -275,12 +275,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -306,12 +306,11 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -626,7 +625,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="44.28515625" style="17" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -643,7 +642,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -672,11 +671,11 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>12375</v>
+        <v>12775</v>
       </c>
       <c r="D2" t="s">
         <v>53</v>
@@ -689,11 +688,11 @@
       </c>
       <c r="H2" s="8">
         <f>C2</f>
-        <v>12375</v>
+        <v>12775</v>
       </c>
       <c r="I2" s="11">
         <f>H2*12</f>
-        <v>148500</v>
+        <v>153300</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>22</v>
@@ -703,11 +702,11 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>7425</v>
+        <v>7665</v>
       </c>
       <c r="D3" t="s">
         <v>53</v>
@@ -718,11 +717,11 @@
       </c>
       <c r="H3" s="8">
         <f>C3</f>
-        <v>7425</v>
+        <v>7665</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" ref="I3:I6" si="0">H3*12</f>
-        <v>89100</v>
+        <v>91980</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>24</v>
@@ -732,11 +731,11 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>10928</v>
+        <v>11398</v>
       </c>
       <c r="D4" t="s">
         <v>53</v>
@@ -761,7 +760,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C5">
@@ -776,11 +775,11 @@
       </c>
       <c r="H5" s="8">
         <f>C4</f>
-        <v>10928</v>
+        <v>11398</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="0"/>
-        <v>131136</v>
+        <v>136776</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>26</v>
@@ -790,7 +789,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C6">
@@ -819,7 +818,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -834,11 +833,11 @@
       </c>
       <c r="H7" s="9">
         <f>SUM(H2:H6)</f>
-        <v>33528</v>
+        <v>34638</v>
       </c>
       <c r="I7" s="9">
         <f>SUM(I2:I6)</f>
-        <v>402336</v>
+        <v>415656</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>29</v>
@@ -848,7 +847,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C8">
@@ -883,7 +882,7 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -910,7 +909,7 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -942,11 +941,11 @@
       <c r="G11" s="7"/>
       <c r="H11" s="9">
         <f>H7-H10</f>
-        <v>31728</v>
+        <v>32838</v>
       </c>
       <c r="I11" s="9">
         <f>I7-I10</f>
-        <v>380736</v>
+        <v>394056</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>38</v>
@@ -1020,7 +1019,7 @@
       </c>
       <c r="I16" s="9">
         <f>SUM(I11:I15)</f>
-        <v>463436</v>
+        <v>476756</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -1063,15 +1062,15 @@
       </c>
       <c r="B2" s="12">
         <f>'Current CTC Breakdown'!I16</f>
-        <v>463436</v>
+        <v>476756</v>
       </c>
       <c r="C2">
         <f>B2/100000</f>
-        <v>4.63436</v>
+        <v>4.7675599999999996</v>
       </c>
       <c r="D2" s="12">
         <f>'Current CTC Breakdown'!H11</f>
-        <v>31728</v>
+        <v>32838</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -1081,15 +1080,15 @@
       </c>
       <c r="B3" s="13">
         <f>$B$2*(1+A3/100)</f>
-        <v>477339.08</v>
+        <v>491058.68</v>
       </c>
       <c r="C3" s="13">
         <f>B3/100000</f>
-        <v>4.7733908000000005</v>
+        <v>4.9105867999999999</v>
       </c>
       <c r="D3" s="13">
         <f>$D$2*(1+A3/100)</f>
-        <v>32679.84</v>
+        <v>33823.14</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1101,15 +1100,15 @@
       </c>
       <c r="B4" s="13">
         <f t="shared" ref="B4:B16" si="0">$B$2*(1+A4/100)</f>
-        <v>481973.44</v>
+        <v>495826.24</v>
       </c>
       <c r="C4" s="13">
         <f t="shared" ref="C4:C16" si="1">B4/100000</f>
-        <v>4.8197343999999998</v>
+        <v>4.9582623999999997</v>
       </c>
       <c r="D4" s="13">
         <f t="shared" ref="D4:D16" si="2">$D$2*(1+A4/100)</f>
-        <v>32997.120000000003</v>
+        <v>34151.520000000004</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1118,15 +1117,15 @@
       </c>
       <c r="B5" s="13">
         <f t="shared" si="0"/>
-        <v>483827.18400000001</v>
+        <v>497733.26400000002</v>
       </c>
       <c r="C5" s="13">
         <f t="shared" si="1"/>
-        <v>4.83827184</v>
+        <v>4.9773326400000002</v>
       </c>
       <c r="D5" s="13">
         <f t="shared" si="2"/>
-        <v>33124.031999999999</v>
+        <v>34282.872000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1135,15 +1134,15 @@
       </c>
       <c r="B6" s="13">
         <f t="shared" si="0"/>
-        <v>486607.80000000005</v>
+        <v>500593.80000000005</v>
       </c>
       <c r="C6" s="13">
         <f t="shared" si="1"/>
-        <v>4.8660780000000008</v>
+        <v>5.0059380000000004</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="2"/>
-        <v>33314.400000000001</v>
+        <v>34479.9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1152,15 +1151,15 @@
       </c>
       <c r="B7" s="13">
         <f t="shared" si="0"/>
-        <v>509779.60000000003</v>
+        <v>524431.60000000009</v>
       </c>
       <c r="C7" s="13">
         <f t="shared" si="1"/>
-        <v>5.0977960000000007</v>
+        <v>5.2443160000000013</v>
       </c>
       <c r="D7" s="13">
         <f t="shared" si="2"/>
-        <v>34900.800000000003</v>
+        <v>36121.800000000003</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1169,34 +1168,33 @@
       </c>
       <c r="B8" s="13">
         <f t="shared" si="0"/>
-        <v>556123.19999999995</v>
+        <v>572107.19999999995</v>
       </c>
       <c r="C8" s="13">
         <f t="shared" si="1"/>
-        <v>5.5612319999999995</v>
+        <v>5.7210719999999995</v>
       </c>
       <c r="D8" s="13">
         <f t="shared" si="2"/>
-        <v>38073.599999999999</v>
+        <v>39405.599999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9">
         <v>30</v>
       </c>
-      <c r="B9" s="16">
-        <f t="shared" si="0"/>
-        <v>602466.80000000005</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="B9" s="15">
+        <f t="shared" si="0"/>
+        <v>619782.80000000005</v>
+      </c>
+      <c r="C9" s="15">
         <f t="shared" si="1"/>
-        <v>6.0246680000000001</v>
-      </c>
-      <c r="D9" s="16">
+        <v>6.1978280000000003</v>
+      </c>
+      <c r="D9" s="15">
         <f t="shared" si="2"/>
-        <v>41246.400000000001</v>
-      </c>
-      <c r="E9" s="15"/>
+        <v>42689.4</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -1204,15 +1202,15 @@
       </c>
       <c r="B10" s="14">
         <f t="shared" si="0"/>
-        <v>648810.39999999991</v>
+        <v>667458.39999999991</v>
       </c>
       <c r="C10" s="14">
         <f t="shared" si="1"/>
-        <v>6.488103999999999</v>
+        <v>6.6745839999999994</v>
       </c>
       <c r="D10" s="14">
         <f t="shared" si="2"/>
-        <v>44419.199999999997</v>
+        <v>45973.2</v>
       </c>
       <c r="E10" s="10"/>
     </row>
@@ -1222,15 +1220,15 @@
       </c>
       <c r="B11" s="14">
         <f t="shared" si="0"/>
-        <v>695154</v>
+        <v>715134</v>
       </c>
       <c r="C11" s="14">
         <f t="shared" si="1"/>
-        <v>6.9515399999999996</v>
+        <v>7.1513400000000003</v>
       </c>
       <c r="D11" s="14">
         <f t="shared" si="2"/>
-        <v>47592</v>
+        <v>49257</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>17</v>
@@ -1242,15 +1240,15 @@
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
-        <v>741497.60000000009</v>
+        <v>762809.60000000009</v>
       </c>
       <c r="C12" s="14">
         <f t="shared" si="1"/>
-        <v>7.4149760000000011</v>
+        <v>7.6280960000000011</v>
       </c>
       <c r="D12" s="14">
         <f t="shared" si="2"/>
-        <v>50764.800000000003</v>
+        <v>52540.800000000003</v>
       </c>
       <c r="E12" s="10"/>
     </row>
@@ -1260,15 +1258,15 @@
       </c>
       <c r="B13" s="13">
         <f t="shared" si="0"/>
-        <v>787841.2</v>
+        <v>810485.2</v>
       </c>
       <c r="C13" s="13">
         <f t="shared" si="1"/>
-        <v>7.878412</v>
+        <v>8.1048519999999993</v>
       </c>
       <c r="D13" s="13">
         <f t="shared" si="2"/>
-        <v>53937.599999999999</v>
+        <v>55824.6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1277,15 +1275,15 @@
       </c>
       <c r="B14" s="13">
         <f t="shared" si="0"/>
-        <v>834184.8</v>
+        <v>858160.8</v>
       </c>
       <c r="C14" s="13">
         <f t="shared" si="1"/>
-        <v>8.3418480000000006</v>
+        <v>8.581608000000001</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="2"/>
-        <v>57110.400000000001</v>
+        <v>59108.4</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1294,15 +1292,15 @@
       </c>
       <c r="B15" s="13">
         <f t="shared" si="0"/>
-        <v>880528.39999999991</v>
+        <v>905836.39999999991</v>
       </c>
       <c r="C15" s="13">
         <f t="shared" si="1"/>
-        <v>8.8052839999999986</v>
+        <v>9.0583639999999992</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="2"/>
-        <v>60283.199999999997</v>
+        <v>62392.2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1311,20 +1309,21 @@
       </c>
       <c r="B16" s="13">
         <f t="shared" si="0"/>
-        <v>926872</v>
+        <v>953512</v>
       </c>
       <c r="C16" s="13">
         <f t="shared" si="1"/>
-        <v>9.2687200000000001</v>
+        <v>9.5351199999999992</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="2"/>
-        <v>63456</v>
+        <v>65676</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
